--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,85 +105,43 @@
     <t>9279-1</t>
   </si>
   <si>
-    <t>Respiratory rate</t>
-  </si>
-  <si>
     <t>8867-4</t>
   </si>
   <si>
-    <t>Heart rate</t>
-  </si>
-  <si>
     <t>2708-6</t>
   </si>
   <si>
-    <t>Oxygen saturation in Arterial blood</t>
-  </si>
-  <si>
     <t>8310-5</t>
   </si>
   <si>
-    <t>Body temperature</t>
-  </si>
-  <si>
     <t>85353-1</t>
   </si>
   <si>
-    <t>Vital signs, weight, height, head circumference, oxygen saturation &amp; BMI panel</t>
-  </si>
-  <si>
     <t>8302-2</t>
   </si>
   <si>
-    <t>Body height</t>
-  </si>
-  <si>
     <t>9843-4</t>
   </si>
   <si>
-    <t>Head Occipital-frontal circumference</t>
-  </si>
-  <si>
     <t>29463-7</t>
   </si>
   <si>
-    <t>Body weight</t>
-  </si>
-  <si>
     <t>39156-5</t>
   </si>
   <si>
-    <t>Body mass index (BMI) [Ratio]</t>
-  </si>
-  <si>
     <t>85354-9</t>
   </si>
   <si>
-    <t>Blood pressure panel with all children optional</t>
-  </si>
-  <si>
     <t>8480-6</t>
   </si>
   <si>
-    <t>Systolic blood pressure</t>
-  </si>
-  <si>
     <t>8462-4</t>
   </si>
   <si>
-    <t>Diastolic blood pressure</t>
-  </si>
-  <si>
     <t>8478-0</t>
   </si>
   <si>
-    <t>Mean blood pressure</t>
-  </si>
-  <si>
     <t>59408-5</t>
-  </si>
-  <si>
-    <t>Oxygen saturation in Arterial blood by Pulse oximetry</t>
   </si>
   <si>
     <t/>
@@ -475,128 +433,100 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>52</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>56</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,43 +105,85 @@
     <t>9279-1</t>
   </si>
   <si>
+    <t>Respiratory rate</t>
+  </si>
+  <si>
     <t>8867-4</t>
   </si>
   <si>
+    <t>Heart rate</t>
+  </si>
+  <si>
     <t>2708-6</t>
   </si>
   <si>
+    <t>Oxygen saturation in Arterial blood</t>
+  </si>
+  <si>
     <t>8310-5</t>
   </si>
   <si>
+    <t>Body temperature</t>
+  </si>
+  <si>
     <t>85353-1</t>
   </si>
   <si>
+    <t>Vital signs, weight, height, head circumference, oxygen saturation &amp; BMI panel</t>
+  </si>
+  <si>
     <t>8302-2</t>
   </si>
   <si>
+    <t>Body height</t>
+  </si>
+  <si>
     <t>9843-4</t>
   </si>
   <si>
+    <t>Head Occipital-frontal circumference</t>
+  </si>
+  <si>
     <t>29463-7</t>
   </si>
   <si>
+    <t>Body weight</t>
+  </si>
+  <si>
     <t>39156-5</t>
   </si>
   <si>
+    <t>Body mass index (BMI) [Ratio]</t>
+  </si>
+  <si>
     <t>85354-9</t>
   </si>
   <si>
+    <t>Blood pressure panel with all children optional</t>
+  </si>
+  <si>
     <t>8480-6</t>
   </si>
   <si>
+    <t>Systolic blood pressure</t>
+  </si>
+  <si>
     <t>8462-4</t>
   </si>
   <si>
+    <t>Diastolic blood pressure</t>
+  </si>
+  <si>
     <t>8478-0</t>
   </si>
   <si>
+    <t>Mean blood pressure</t>
+  </si>
+  <si>
     <t>59408-5</t>
+  </si>
+  <si>
+    <t>Oxygen saturation in Arterial blood by Pulse oximetry</t>
   </si>
   <si>
     <t/>
@@ -433,100 +475,128 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,85 +105,43 @@
     <t>9279-1</t>
   </si>
   <si>
-    <t>Respiratory rate</t>
-  </si>
-  <si>
     <t>8867-4</t>
   </si>
   <si>
-    <t>Heart rate</t>
-  </si>
-  <si>
     <t>2708-6</t>
   </si>
   <si>
-    <t>Oxygen saturation in Arterial blood</t>
-  </si>
-  <si>
     <t>8310-5</t>
   </si>
   <si>
-    <t>Body temperature</t>
-  </si>
-  <si>
     <t>85353-1</t>
   </si>
   <si>
-    <t>Vital signs, weight, height, head circumference, oxygen saturation &amp; BMI panel</t>
-  </si>
-  <si>
     <t>8302-2</t>
   </si>
   <si>
-    <t>Body height</t>
-  </si>
-  <si>
     <t>9843-4</t>
   </si>
   <si>
-    <t>Head Occipital-frontal circumference</t>
-  </si>
-  <si>
     <t>29463-7</t>
   </si>
   <si>
-    <t>Body weight</t>
-  </si>
-  <si>
     <t>39156-5</t>
   </si>
   <si>
-    <t>Body mass index (BMI) [Ratio]</t>
-  </si>
-  <si>
     <t>85354-9</t>
   </si>
   <si>
-    <t>Blood pressure panel with all children optional</t>
-  </si>
-  <si>
     <t>8480-6</t>
   </si>
   <si>
-    <t>Systolic blood pressure</t>
-  </si>
-  <si>
     <t>8462-4</t>
   </si>
   <si>
-    <t>Diastolic blood pressure</t>
-  </si>
-  <si>
     <t>8478-0</t>
   </si>
   <si>
-    <t>Mean blood pressure</t>
-  </si>
-  <si>
     <t>59408-5</t>
-  </si>
-  <si>
-    <t>Oxygen saturation in Arterial blood by Pulse oximetry</t>
   </si>
   <si>
     <t/>
@@ -475,128 +433,100 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>52</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>56</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from LOINC" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,43 +105,85 @@
     <t>9279-1</t>
   </si>
   <si>
+    <t>Respiratory rate</t>
+  </si>
+  <si>
     <t>8867-4</t>
   </si>
   <si>
+    <t>Heart rate</t>
+  </si>
+  <si>
     <t>2708-6</t>
   </si>
   <si>
+    <t>Oxygen saturation in Arterial blood</t>
+  </si>
+  <si>
     <t>8310-5</t>
   </si>
   <si>
+    <t>Body temperature</t>
+  </si>
+  <si>
     <t>85353-1</t>
   </si>
   <si>
+    <t>Vital signs, weight, height, head circumference, oxygen saturation &amp; BMI panel</t>
+  </si>
+  <si>
     <t>8302-2</t>
   </si>
   <si>
+    <t>Body height</t>
+  </si>
+  <si>
     <t>9843-4</t>
   </si>
   <si>
+    <t>Head Occipital-frontal circumference</t>
+  </si>
+  <si>
     <t>29463-7</t>
   </si>
   <si>
+    <t>Body weight</t>
+  </si>
+  <si>
     <t>39156-5</t>
   </si>
   <si>
+    <t>Body mass index (BMI) [Ratio]</t>
+  </si>
+  <si>
     <t>85354-9</t>
   </si>
   <si>
+    <t>Blood pressure panel with all children optional</t>
+  </si>
+  <si>
     <t>8480-6</t>
   </si>
   <si>
+    <t>Systolic blood pressure</t>
+  </si>
+  <si>
     <t>8462-4</t>
   </si>
   <si>
+    <t>Diastolic blood pressure</t>
+  </si>
+  <si>
     <t>8478-0</t>
   </si>
   <si>
+    <t>Mean blood pressure</t>
+  </si>
+  <si>
     <t>59408-5</t>
+  </si>
+  <si>
+    <t>Oxygen saturation in Arterial blood by Pulse oximetry</t>
   </si>
   <si>
     <t/>
@@ -433,100 +475,128 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,85 +105,43 @@
     <t>9279-1</t>
   </si>
   <si>
-    <t>Respiratory rate</t>
-  </si>
-  <si>
     <t>8867-4</t>
   </si>
   <si>
-    <t>Heart rate</t>
-  </si>
-  <si>
     <t>2708-6</t>
   </si>
   <si>
-    <t>Oxygen saturation in Arterial blood</t>
-  </si>
-  <si>
     <t>8310-5</t>
   </si>
   <si>
-    <t>Body temperature</t>
-  </si>
-  <si>
     <t>85353-1</t>
   </si>
   <si>
-    <t>Vital signs, weight, height, head circumference, oxygen saturation &amp; BMI panel</t>
-  </si>
-  <si>
     <t>8302-2</t>
   </si>
   <si>
-    <t>Body height</t>
-  </si>
-  <si>
     <t>9843-4</t>
   </si>
   <si>
-    <t>Head Occipital-frontal circumference</t>
-  </si>
-  <si>
     <t>29463-7</t>
   </si>
   <si>
-    <t>Body weight</t>
-  </si>
-  <si>
     <t>39156-5</t>
   </si>
   <si>
-    <t>Body mass index (BMI) [Ratio]</t>
-  </si>
-  <si>
     <t>85354-9</t>
   </si>
   <si>
-    <t>Blood pressure panel with all children optional</t>
-  </si>
-  <si>
     <t>8480-6</t>
   </si>
   <si>
-    <t>Systolic blood pressure</t>
-  </si>
-  <si>
     <t>8462-4</t>
   </si>
   <si>
-    <t>Diastolic blood pressure</t>
-  </si>
-  <si>
     <t>8478-0</t>
   </si>
   <si>
-    <t>Mean blood pressure</t>
-  </si>
-  <si>
     <t>59408-5</t>
-  </si>
-  <si>
-    <t>Oxygen saturation in Arterial blood by Pulse oximetry</t>
   </si>
   <si>
     <t/>
@@ -475,128 +433,100 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>52</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>56</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,43 +105,85 @@
     <t>9279-1</t>
   </si>
   <si>
+    <t>Respiratory rate</t>
+  </si>
+  <si>
     <t>8867-4</t>
   </si>
   <si>
+    <t>Heart rate</t>
+  </si>
+  <si>
     <t>2708-6</t>
   </si>
   <si>
+    <t>Oxygen saturation in Arterial blood</t>
+  </si>
+  <si>
     <t>8310-5</t>
   </si>
   <si>
+    <t>Body temperature</t>
+  </si>
+  <si>
     <t>85353-1</t>
   </si>
   <si>
+    <t>Vital signs, weight, height, head circumference, oxygen saturation &amp; BMI panel</t>
+  </si>
+  <si>
     <t>8302-2</t>
   </si>
   <si>
+    <t>Body height</t>
+  </si>
+  <si>
     <t>9843-4</t>
   </si>
   <si>
+    <t>Head Occipital-frontal circumference</t>
+  </si>
+  <si>
     <t>29463-7</t>
   </si>
   <si>
+    <t>Body weight</t>
+  </si>
+  <si>
     <t>39156-5</t>
   </si>
   <si>
+    <t>Body mass index (BMI) [Ratio]</t>
+  </si>
+  <si>
     <t>85354-9</t>
   </si>
   <si>
+    <t>Blood pressure panel with all children optional</t>
+  </si>
+  <si>
     <t>8480-6</t>
   </si>
   <si>
+    <t>Systolic blood pressure</t>
+  </si>
+  <si>
     <t>8462-4</t>
   </si>
   <si>
+    <t>Diastolic blood pressure</t>
+  </si>
+  <si>
     <t>8478-0</t>
   </si>
   <si>
+    <t>Mean blood pressure</t>
+  </si>
+  <si>
     <t>59408-5</t>
+  </si>
+  <si>
+    <t>Oxygen saturation in Arterial blood by Pulse oximetry</t>
   </si>
   <si>
     <t/>
@@ -433,100 +475,128 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-LoincBasicObservation.xlsx
+++ b/ValueSet-dk-core-LoincBasicObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
